--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -23125,16 +23125,16 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O137" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0.1647274435223239</v>
+        <v>0.168603383369908</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -24065,16 +24065,16 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O142" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0.2390130845540293</v>
+        <v>0.2433587770004662</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26633,16 +26633,16 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.04780261691080586</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4738</v>
+        <v>4743</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -24613,16 +24613,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O143" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1647274435223239</v>
+        <v>0.1666654134461159</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25553,16 +25553,16 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O148" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.2477044694469031</v>
+        <v>0.25205016189334</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -27577,16 +27577,16 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O161" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.04069736839963296</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -28121,16 +28121,16 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O164" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>0.06083969425011655</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28347,6 +28347,154 @@
       <c r="BC165" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>53</v>
+      </c>
+      <c r="O166" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28383,7 +28531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28614,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -28476,7 +28624,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -28528,7 +28676,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4745</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>38</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.4218567068222445</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>68</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.1317819548178591</v>
       </c>
@@ -2146,9 +2131,6 @@
       <c r="O10" t="n">
         <v>9</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1592078243215956</v>
       </c>
@@ -2791,7 +2773,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2920,6 @@
       <c r="O14" t="n">
         <v>7</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.06541416299798342</v>
       </c>
@@ -4962,9 +4941,6 @@
       <c r="O27" t="n">
         <v>13</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5355,9 +5331,6 @@
       <c r="O29" t="n">
         <v>24</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.2664358148351018</v>
       </c>
@@ -5503,9 +5476,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -5899,9 +5869,6 @@
       <c r="O32" t="n">
         <v>4</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -6047,9 +6014,6 @@
       <c r="O33" t="n">
         <v>68</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.1317819548178591</v>
       </c>
@@ -6195,9 +6159,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6840,7 +6801,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -6987,9 +6948,6 @@
       <c r="O38" t="n">
         <v>5</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -8863,9 +8821,6 @@
       <c r="O50" t="n">
         <v>17</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9256,9 +9211,6 @@
       <c r="O52" t="n">
         <v>30</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.3330447685438772</v>
       </c>
@@ -9404,9 +9356,6 @@
       <c r="O53" t="n">
         <v>4</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.07115236683456549</v>
       </c>
@@ -9800,9 +9749,6 @@
       <c r="O55" t="n">
         <v>10</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.1355270280196709</v>
       </c>
@@ -9948,9 +9894,6 @@
       <c r="O56" t="n">
         <v>53</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.1027124059609784</v>
       </c>
@@ -10096,9 +10039,6 @@
       <c r="O57" t="n">
         <v>3</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -10741,7 +10681,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -10888,9 +10828,6 @@
       <c r="O61" t="n">
         <v>11</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.1027936847111168</v>
       </c>
@@ -12616,9 +12553,6 @@
       <c r="O72" t="n">
         <v>42</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.1542580964198312</v>
       </c>
@@ -12764,9 +12698,6 @@
       <c r="O73" t="n">
         <v>26</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13157,9 +13088,6 @@
       <c r="O75" t="n">
         <v>21</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.2331313379807141</v>
       </c>
@@ -13305,9 +13233,6 @@
       <c r="O76" t="n">
         <v>6</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -13701,9 +13626,6 @@
       <c r="O78" t="n">
         <v>19</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.2575013532373748</v>
       </c>
@@ -13849,9 +13771,6 @@
       <c r="O79" t="n">
         <v>54</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1046503758847705</v>
       </c>
@@ -13997,9 +13916,6 @@
       <c r="O80" t="n">
         <v>3</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -14393,9 +14309,6 @@
       <c r="O82" t="n">
         <v>13</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2458638606413378</v>
       </c>
@@ -14642,7 +14555,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -14789,9 +14702,6 @@
       <c r="O84" t="n">
         <v>6</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -15185,9 +15095,6 @@
       <c r="O86" t="n">
         <v>66</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.2868157014648351</v>
       </c>
@@ -16517,9 +16424,6 @@
       <c r="O95" t="n">
         <v>57</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.209350273712628</v>
       </c>
@@ -16665,9 +16569,6 @@
       <c r="O96" t="n">
         <v>24</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17058,9 +16959,6 @@
       <c r="O98" t="n">
         <v>44</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.4884656605310199</v>
       </c>
@@ -17206,9 +17104,6 @@
       <c r="O99" t="n">
         <v>7</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -17602,9 +17497,6 @@
       <c r="O101" t="n">
         <v>28</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.3794756784550786</v>
       </c>
@@ -17750,9 +17642,6 @@
       <c r="O102" t="n">
         <v>57</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.1104642856561466</v>
       </c>
@@ -17898,9 +17787,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -18294,9 +18180,6 @@
       <c r="O105" t="n">
         <v>13</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.2458638606413378</v>
       </c>
@@ -18543,7 +18426,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -18690,9 +18573,6 @@
       <c r="O107" t="n">
         <v>8</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.07475904342626677</v>
       </c>
@@ -19086,9 +18966,6 @@
       <c r="O109" t="n">
         <v>77</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.334618318375641</v>
       </c>
@@ -20566,9 +20443,6 @@
       <c r="O119" t="n">
         <v>44</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01260616778418529</v>
       </c>
@@ -20714,9 +20588,6 @@
       <c r="O120" t="n">
         <v>48</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1762949673369499</v>
       </c>
@@ -20862,9 +20733,6 @@
       <c r="O121" t="n">
         <v>3</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -21258,9 +21126,6 @@
       <c r="O123" t="n">
         <v>19</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.2575013532373748</v>
       </c>
@@ -21406,9 +21271,6 @@
       <c r="O124" t="n">
         <v>57</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.1104642856561466</v>
       </c>
@@ -21554,9 +21416,6 @@
       <c r="O125" t="n">
         <v>5</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -21950,9 +21809,6 @@
       <c r="O127" t="n">
         <v>7</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -22199,7 +22055,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -22346,9 +22202,6 @@
       <c r="O129" t="n">
         <v>13</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.1214834455676835</v>
       </c>
@@ -22742,9 +22595,6 @@
       <c r="O131" t="n">
         <v>59</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.2563958543397769</v>
       </c>
@@ -22890,9 +22740,6 @@
       <c r="O132" t="n">
         <v>34</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.02777148585723605</v>
       </c>
@@ -23038,9 +22885,6 @@
       <c r="O133" t="n">
         <v>89</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.02549883938164753</v>
       </c>
@@ -23186,9 +23030,6 @@
       <c r="O134" t="n">
         <v>44</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.03593956993289372</v>
       </c>
@@ -23334,9 +23175,6 @@
       <c r="O135" t="n">
         <v>78</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.02234729743560121</v>
       </c>
@@ -23482,9 +23320,6 @@
       <c r="O136" t="n">
         <v>40</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.03267233630263065</v>
       </c>
@@ -23630,9 +23465,6 @@
       <c r="O137" t="n">
         <v>41</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.01174665634435448</v>
       </c>
@@ -23778,9 +23610,6 @@
       <c r="O138" t="n">
         <v>68</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.05554297171447211</v>
       </c>
@@ -23926,9 +23755,6 @@
       <c r="O139" t="n">
         <v>65</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.018622747863001</v>
       </c>
@@ -24074,9 +23900,6 @@
       <c r="O140" t="n">
         <v>24</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.08814748366847497</v>
       </c>
@@ -24222,9 +24045,6 @@
       <c r="O141" t="n">
         <v>5</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -24613,16 +24433,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O143" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1666654134461159</v>
+        <v>0.1705413532937</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24761,16 +24578,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O144" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R144" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24923,10 +24737,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -25162,9 +24976,6 @@
       <c r="O146" t="n">
         <v>28</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.2616566519919337</v>
       </c>
@@ -25558,9 +25369,6 @@
       <c r="O148" t="n">
         <v>58</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.25205016189334</v>
       </c>
@@ -25706,9 +25514,6 @@
       <c r="O149" t="n">
         <v>51</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.04165722878585408</v>
       </c>
@@ -25854,9 +25659,6 @@
       <c r="O150" t="n">
         <v>85</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.02435282412853977</v>
       </c>
@@ -26002,9 +25804,6 @@
       <c r="O151" t="n">
         <v>83</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.0677950978279586</v>
       </c>
@@ -26150,9 +25949,6 @@
       <c r="O152" t="n">
         <v>153</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0438350834313716</v>
       </c>
@@ -26298,9 +26094,6 @@
       <c r="O153" t="n">
         <v>141</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.1151699854667731</v>
       </c>
@@ -26446,9 +26239,6 @@
       <c r="O154" t="n">
         <v>65</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.018622747863001</v>
       </c>
@@ -26594,9 +26384,6 @@
       <c r="O155" t="n">
         <v>83</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.0677950978279586</v>
       </c>
@@ -26742,9 +26529,6 @@
       <c r="O156" t="n">
         <v>107</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.03065590802063242</v>
       </c>
@@ -26890,9 +26674,6 @@
       <c r="O157" t="n">
         <v>68</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.05554297171447211</v>
       </c>
@@ -27038,9 +26819,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27181,16 +26959,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R159" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27343,10 +27118,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -27582,9 +27357,6 @@
       <c r="O161" t="n">
         <v>21</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.04069736839963296</v>
       </c>
@@ -27725,16 +27497,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O162" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R162" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27887,10 +27656,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -28121,16 +27890,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O164" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R164" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.06083969425011655</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28274,9 +28040,6 @@
       <c r="O165" t="n">
         <v>71</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.02034177074266263</v>
       </c>
@@ -28422,9 +28185,6 @@
       <c r="O166" t="n">
         <v>53</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.04329084560098561</v>
       </c>
@@ -28495,6 +28255,151 @@
       <c r="BC166" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>92</v>
+      </c>
+      <c r="O167" t="n">
+        <v>92</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.02635835082147835</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28531,7 +28436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -28614,7 +28519,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -28624,7 +28529,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28676,7 +28581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4803</v>
+        <v>4902</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -27890,13 +27890,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O164" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R164" t="n">
-        <v>0.06083969425011655</v>
+        <v>0.06518538669655344</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4902</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -20583,13 +20583,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O120" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R120" t="n">
-        <v>0.1762949673369499</v>
+        <v>0.1726221555174302</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23895,13 +23895,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="O140" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="R140" t="n">
-        <v>0.08814748366847497</v>
+        <v>0.1138571664051135</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4903</v>
+        <v>4909</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -16564,10 +16564,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O96" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16720,10 +16720,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O97" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -20689,12 +20689,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20728,22 +20728,19 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="O121" t="n">
-        <v>3</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.05336427512592412</v>
+        <v>49</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_CA_ON_PHO_IDTO_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -20763,12 +20760,12 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_CA_ON_PHO_IDTO_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -20776,47 +20773,47 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20848,12 +20845,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20887,24 +20884,24 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="O122" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_CA_ON_PHO_IDTO_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_CA_ON_PHO_IDTO_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -20919,7 +20916,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -20934,7 +20931,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -20969,17 +20966,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+          <t>PHO IDTO current-year monthly preliminary legionellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -20997,12 +20994,12 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_CA_ON_PHO_IDTO_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -21010,47 +21007,47 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21082,12 +21079,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21121,81 +21118,95 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="R123" t="n">
-        <v>0.2575013532373748</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21222,17 +21233,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21266,81 +21277,170 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="O124" t="n">
-        <v>57</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0.1104642856561466</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21372,12 +21472,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21411,95 +21511,81 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="O125" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R125" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.2575013532373748</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21526,17 +21612,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21570,170 +21656,81 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="O126" t="n">
-        <v>5</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.1104642856561466</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21765,12 +21762,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21804,13 +21801,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O127" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R127" t="n">
-        <v>0.132388232653028</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21819,7 +21816,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -21844,7 +21841,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -21857,42 +21854,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21924,12 +21921,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21963,29 +21960,29 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Legionellose</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -21995,7 +21992,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -22010,7 +22007,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -22045,17 +22042,17 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -22078,7 +22075,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22091,42 +22088,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22158,12 +22155,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22197,13 +22194,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R129" t="n">
-        <v>0.1214834455676835</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22212,7 +22209,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -22237,7 +22234,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22250,42 +22247,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22317,12 +22314,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22356,29 +22353,29 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O130" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>Legionellainfektion</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -22388,7 +22385,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -22403,7 +22400,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -22438,17 +22435,17 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -22471,7 +22468,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -22484,42 +22481,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22551,12 +22548,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22590,81 +22587,95 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="O131" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="R131" t="n">
-        <v>0.2563958543397769</v>
+        <v>0.1214834455676835</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22691,17 +22702,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22726,7 +22737,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22735,81 +22746,170 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="O132" t="n">
-        <v>34</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0.02777148585723605</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22941,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22871,7 +22971,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22880,13 +22980,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="O133" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="R133" t="n">
-        <v>0.02549883938164753</v>
+        <v>0.2563958543397769</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22919,42 +23019,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23116,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23025,13 +23125,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="O134" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R134" t="n">
-        <v>0.03593956993289372</v>
+        <v>0.02777148585723605</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23161,7 +23261,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23170,13 +23270,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="O135" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="R135" t="n">
-        <v>0.02234729743560121</v>
+        <v>0.02549883938164753</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23306,7 +23406,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23315,13 +23415,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O136" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R136" t="n">
-        <v>0.03267233630263065</v>
+        <v>0.03593956993289372</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23451,7 +23551,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23460,13 +23560,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="O137" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="R137" t="n">
-        <v>0.01174665634435448</v>
+        <v>0.02234729743560121</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23596,7 +23696,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23605,13 +23705,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="O138" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="R138" t="n">
-        <v>0.05554297171447211</v>
+        <v>0.03267233630263065</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23741,7 +23841,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23750,13 +23850,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="O139" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="R139" t="n">
-        <v>0.018622747863001</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23856,12 +23956,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23886,22 +23986,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="O140" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="R140" t="n">
-        <v>0.1138571664051135</v>
+        <v>0.05554297171447211</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23934,42 +24034,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24001,12 +24101,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24031,104 +24131,90 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="R141" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24155,17 +24241,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24199,170 +24285,81 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="O142" t="n">
-        <v>5</v>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.1138571664051135</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV142" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24394,12 +24391,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24433,81 +24430,95 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="O143" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1705413532937</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24534,17 +24545,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24578,22 +24589,39 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O144" t="n">
-        <v>7</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.1238283078056854</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -24601,6 +24629,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24613,12 +24699,12 @@
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -24626,47 +24712,47 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24693,17 +24779,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24737,170 +24823,81 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
+        <v>88</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.1705413532937</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24932,12 +24929,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24971,13 +24968,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O146" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="R146" t="n">
-        <v>0.2616566519919337</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24986,7 +24983,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -25011,7 +25008,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -25024,42 +25021,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25088,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25130,29 +25127,29 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Legionellainfektion</t>
+          <t>Legionellose</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -25177,7 +25174,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -25212,17 +25209,17 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -25245,7 +25242,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -25258,42 +25255,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25325,12 +25322,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25364,81 +25361,95 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="O148" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="R148" t="n">
-        <v>0.25205016189334</v>
+        <v>0.2616566519919337</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25465,17 +25476,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25500,7 +25511,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25509,81 +25520,170 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O149" t="n">
-        <v>51</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0.04165722878585408</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25615,12 +25715,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25645,7 +25745,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25654,13 +25754,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="O150" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="R150" t="n">
-        <v>0.02435282412853977</v>
+        <v>0.25205016189334</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25693,42 +25793,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25790,7 +25890,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25799,13 +25899,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="O151" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.04165722878585408</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25935,7 +26035,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25944,13 +26044,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="O152" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="R152" t="n">
-        <v>0.0438350834313716</v>
+        <v>0.02435282412853977</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26080,7 +26180,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26089,13 +26189,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="O153" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1151699854667731</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26225,7 +26325,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26234,13 +26334,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="O154" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="R154" t="n">
-        <v>0.018622747863001</v>
+        <v>0.0438350834313716</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26370,7 +26470,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26379,13 +26479,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="O155" t="n">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="R155" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.1151699854667731</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26515,7 +26615,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26524,13 +26624,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="O156" t="n">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="R156" t="n">
-        <v>0.03065590802063242</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26660,7 +26760,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26669,13 +26769,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="O157" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="R157" t="n">
-        <v>0.05554297171447211</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26775,12 +26875,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26805,22 +26905,22 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>0.03065590802063242</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -26853,42 +26953,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26920,12 +27020,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26950,104 +27050,90 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="O159" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="R159" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05554297171447211</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27074,17 +27160,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27118,170 +27204,81 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O160" t="n">
-        <v>2</v>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.02203687091711874</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV160" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27313,12 +27310,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27352,81 +27349,95 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R161" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27453,17 +27464,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27502,17 +27513,34 @@
       <c r="O162" t="n">
         <v>2</v>
       </c>
-      <c r="R162" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -27520,6 +27548,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27532,12 +27618,12 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -27545,47 +27631,47 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27612,17 +27698,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27656,170 +27742,81 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O163" t="n">
-        <v>2</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.04069736839963296</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27851,12 +27848,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27890,81 +27887,95 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O164" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R164" t="n">
-        <v>0.06518538669655344</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27991,17 +28002,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28035,81 +28046,170 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="O165" t="n">
-        <v>71</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.02034177074266263</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28141,12 +28241,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28171,7 +28271,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28180,13 +28280,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="O166" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="R166" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.06518538669655344</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28219,42 +28319,42 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28316,7 +28416,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28325,13 +28425,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="O167" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="R167" t="n">
-        <v>0.02635835082147835</v>
+        <v>0.02034177074266263</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -28398,6 +28498,296 @@
         </is>
       </c>
       <c r="BC167" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>53</v>
+      </c>
+      <c r="O168" t="n">
+        <v>53</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>92</v>
+      </c>
+      <c r="O169" t="n">
+        <v>92</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.02635835082147835</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -28519,7 +28909,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -28529,7 +28919,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -28549,7 +28939,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -28581,7 +28971,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4909</v>
+        <v>4965</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O150" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R150" t="n">
-        <v>0.25205016189334</v>
+        <v>0.2563958543397769</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -28280,13 +28280,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O166" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R166" t="n">
-        <v>0.06518538669655344</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4965</v>
+        <v>4969</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -24823,13 +24823,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O145" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R145" t="n">
-        <v>0.1705413532937</v>
+        <v>0.168603383369908</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O160" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R160" t="n">
-        <v>0.02203687091711874</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27742,13 +27742,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="O163" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="R163" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.06589097740892956</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28790,6 +28790,151 @@
       <c r="BC169" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>60</v>
+      </c>
+      <c r="O170" t="n">
+        <v>60</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.04900850445394597</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28826,7 +28971,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -28909,7 +29054,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -28919,7 +29064,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -28971,7 +29116,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4969</v>
+        <v>5047</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O142" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1138571664051135</v>
+        <v>0.1175299782246333</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O160" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R160" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.06243780093183643</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27887,13 +27887,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R164" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U165" t="inlineStr">
         <is>
@@ -28935,6 +28935,151 @@
       <c r="BC170" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>134</v>
+      </c>
+      <c r="O171" t="n">
+        <v>134</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.03839151097910976</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28971,7 +29116,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29199,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -29064,7 +29209,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -29116,7 +29261,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5047</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O160" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R160" t="n">
-        <v>0.06243780093183643</v>
+        <v>0.07345623639039579</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27508,10 +27508,10 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5188</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O142" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1175299782246333</v>
+        <v>0.1212027900441531</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O160" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R160" t="n">
-        <v>0.07345623639039579</v>
+        <v>0.07712904820991559</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5192</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -20583,13 +20583,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O120" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R120" t="n">
-        <v>0.1726221555174302</v>
+        <v>0.1762949673369499</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -21656,13 +21656,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O126" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R126" t="n">
-        <v>0.1104642856561466</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O142" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1212027900441531</v>
+        <v>0.1322212255027125</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24823,13 +24823,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O145" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="R145" t="n">
-        <v>0.168603383369908</v>
+        <v>0.1821691728364523</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25322,12 +25322,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25361,13 +25361,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="O148" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="R148" t="n">
-        <v>0.2616566519919337</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -25414,42 +25414,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25520,29 +25520,29 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="O149" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Legionellainfektion</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -25552,7 +25552,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -25602,17 +25602,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -25648,42 +25648,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25715,12 +25715,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25754,81 +25754,95 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="O150" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="R150" t="n">
-        <v>0.2563958543397769</v>
+        <v>0.2616566519919337</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25855,17 +25869,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25890,7 +25904,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25899,81 +25913,170 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O151" t="n">
-        <v>51</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0.04165722878585408</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26005,12 +26108,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26035,7 +26138,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26044,13 +26147,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="O152" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="R152" t="n">
-        <v>0.02435282412853977</v>
+        <v>0.2563958543397769</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26083,42 +26186,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26180,7 +26283,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26189,13 +26292,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="O153" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="R153" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.04165722878585408</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26325,7 +26428,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26334,13 +26437,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="O154" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="R154" t="n">
-        <v>0.0438350834313716</v>
+        <v>0.02435282412853977</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26470,7 +26573,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26479,13 +26582,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="O155" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1151699854667731</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26615,7 +26718,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26624,13 +26727,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="O156" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="R156" t="n">
-        <v>0.018622747863001</v>
+        <v>0.0438350834313716</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26760,7 +26863,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26769,13 +26872,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="O157" t="n">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="R157" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.1151699854667731</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26905,7 +27008,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -26914,13 +27017,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="O158" t="n">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="R158" t="n">
-        <v>0.03065590802063242</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27050,7 +27153,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27059,13 +27162,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="O159" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="R159" t="n">
-        <v>0.05554297171447211</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27165,12 +27268,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27195,22 +27298,22 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="O160" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="R160" t="n">
-        <v>0.07712904820991559</v>
+        <v>0.03065590802063242</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27243,42 +27346,42 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27310,12 +27413,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27340,104 +27443,90 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="O161" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="R161" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.05554297171447211</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27464,17 +27553,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27508,170 +27597,81 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="O162" t="n">
-        <v>3</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.1285484136831927</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV162" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27703,12 +27703,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27742,81 +27742,95 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="O163" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="R163" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27843,17 +27857,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27892,17 +27906,34 @@
       <c r="O164" t="n">
         <v>3</v>
       </c>
-      <c r="R164" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -27910,6 +27941,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27922,12 +28011,12 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -27935,47 +28024,47 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28002,17 +28091,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28046,170 +28135,81 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="O165" t="n">
-        <v>3</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.08720864657064206</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28241,12 +28241,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28280,81 +28280,95 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O166" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="R166" t="n">
-        <v>0.07822246403586412</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28381,17 +28395,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28425,81 +28439,170 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="O167" t="n">
-        <v>71</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0.02034177074266263</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28531,12 +28634,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28561,7 +28664,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28570,13 +28673,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="O168" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="R168" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28609,42 +28712,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28809,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28715,13 +28818,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="O169" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="R169" t="n">
-        <v>0.02635835082147835</v>
+        <v>0.02034177074266263</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -28851,7 +28954,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28860,13 +28963,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O170" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="R170" t="n">
-        <v>0.04900850445394597</v>
+        <v>0.04329084560098561</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28996,7 +29099,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -29005,13 +29108,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="O171" t="n">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="R171" t="n">
-        <v>0.03839151097910976</v>
+        <v>0.02635835082147835</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -29080,6 +29183,441 @@
       <c r="BC171" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>60</v>
+      </c>
+      <c r="O172" t="n">
+        <v>60</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.04900850445394597</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>134</v>
+      </c>
+      <c r="O173" t="n">
+        <v>134</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.03839151097910976</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>45</v>
+      </c>
+      <c r="O174" t="n">
+        <v>45</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.03675637834045948</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29116,7 +29654,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29737,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -29209,7 +29747,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -29229,7 +29767,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -29261,7 +29799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5194</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O142" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1322212255027125</v>
+        <v>0.1358940373222322</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24823,13 +24823,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O145" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R145" t="n">
-        <v>0.1821691728364523</v>
+        <v>0.1782932329888682</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -27597,13 +27597,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O162" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R162" t="n">
-        <v>0.1285484136831927</v>
+        <v>0.1138571664051135</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -28135,13 +28135,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O165" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R165" t="n">
-        <v>0.08720864657064206</v>
+        <v>0.09108458641822616</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5287</v>
+        <v>5284</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -35028,12 +35028,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35067,13 +35067,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="O197" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="R197" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.2710540560393419</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -35106,42 +35106,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35173,12 +35173,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35212,95 +35212,81 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="O198" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="R198" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35327,7 +35313,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -35376,98 +35362,23 @@
       <c r="O199" t="n">
         <v>7</v>
       </c>
+      <c r="R199" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -35561,17 +35472,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35605,22 +35516,39 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O200" t="n">
-        <v>10</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0.1891260466471829</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -35628,6 +35556,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35645,7 +35631,7 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -35658,42 +35644,42 @@
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35720,7 +35706,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -35769,98 +35755,23 @@
       <c r="O201" t="n">
         <v>10</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.1891260466471829</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -35954,17 +35865,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35998,22 +35909,39 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="O202" t="n">
-        <v>28</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.2616566519919337</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -36021,6 +35949,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36038,7 +36024,7 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -36051,42 +36037,42 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36113,7 +36099,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -36162,98 +36148,23 @@
       <c r="O203" t="n">
         <v>28</v>
       </c>
+      <c r="R203" t="n">
+        <v>0.2616566519919337</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Legionellainfektion</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -36347,17 +36258,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36391,81 +36302,170 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="O204" t="n">
-        <v>59</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.2563958543397769</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36497,12 +36497,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36527,7 +36527,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36536,13 +36536,13 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="O205" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="R205" t="n">
-        <v>0.04165722878585408</v>
+        <v>0.2563958543397769</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -36575,42 +36575,42 @@
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36642,12 +36642,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36681,13 +36681,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="O206" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="R206" t="n">
-        <v>0.02435282412853977</v>
+        <v>0.04165722878585408</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -36720,42 +36720,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36787,12 +36787,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -36826,93 +36826,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="O207" t="n">
-        <v>3</v>
-      </c>
-      <c r="P207" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="R207" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.02435282412853977</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36939,7 +36927,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -36991,98 +36979,18 @@
       <c r="P208" t="n">
         <v>3</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -37176,17 +37084,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -37211,7 +37119,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -37220,81 +37128,173 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="O209" t="n">
-        <v>83</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.0677950978279586</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P209" t="n">
+        <v>3</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37326,12 +37326,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37365,13 +37365,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="O210" t="n">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="R210" t="n">
-        <v>0.0438350834313716</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -37404,42 +37404,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37471,12 +37471,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37510,93 +37510,81 @@
         </is>
       </c>
       <c r="N211" t="n">
+        <v>153</v>
+      </c>
+      <c r="O211" t="n">
+        <v>153</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.0438350834313716</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="n">
         <v>0</v>
       </c>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP211" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT211" t="n">
-        <v>2</v>
-      </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37623,7 +37611,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -37675,98 +37663,18 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -37860,17 +37768,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37895,7 +37803,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -37904,81 +37812,173 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>141</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.1151699854667731</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38010,12 +38010,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38049,13 +38049,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="O214" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="R214" t="n">
-        <v>0.018622747863001</v>
+        <v>0.1151699854667731</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -38088,42 +38088,42 @@
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38155,12 +38155,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -38185,7 +38185,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -38194,93 +38194,81 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="O215" t="n">
-        <v>2</v>
-      </c>
-      <c r="P215" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="R215" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38307,7 +38295,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -38359,98 +38347,18 @@
       <c r="P216" t="n">
         <v>2</v>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R216" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -38544,17 +38452,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38579,7 +38487,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -38588,81 +38496,173 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="O217" t="n">
-        <v>83</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.0677950978279586</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P217" t="n">
+        <v>2</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38694,12 +38694,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38733,13 +38733,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="O218" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="R218" t="n">
-        <v>0.03065590802063242</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -38772,42 +38772,42 @@
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38839,12 +38839,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -38869,7 +38869,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -38878,13 +38878,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="O219" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="R219" t="n">
-        <v>0.05554297171447211</v>
+        <v>0.03065590802063242</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -38917,42 +38917,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38984,12 +38984,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39023,93 +39023,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="O220" t="n">
-        <v>2</v>
-      </c>
-      <c r="P220" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="R220" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05554297171447211</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39136,7 +39124,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -39188,98 +39176,18 @@
       <c r="P221" t="n">
         <v>2</v>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R221" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -39373,17 +39281,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39408,90 +39316,182 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="O222" t="n">
-        <v>31</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0.1138571664051135</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P222" t="n">
+        <v>2</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39523,12 +39523,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39562,95 +39562,81 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="O223" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="R223" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.1138571664051135</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39677,7 +39663,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -39726,98 +39712,23 @@
       <c r="O224" t="n">
         <v>3</v>
       </c>
+      <c r="R224" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -39911,17 +39822,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -39955,81 +39866,170 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="O225" t="n">
-        <v>47</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.09108458641822616</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40061,12 +40061,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40100,95 +40100,81 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="O226" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="R226" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.09883646611339433</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40215,7 +40201,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -40264,98 +40250,23 @@
       <c r="O227" t="n">
         <v>3</v>
       </c>
+      <c r="R227" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -40449,17 +40360,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40493,81 +40404,170 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O228" t="n">
-        <v>18</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.07822246403586412</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40599,12 +40599,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40638,13 +40638,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="O229" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="R229" t="n">
-        <v>0.02034177074266263</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -40677,42 +40677,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -40744,12 +40744,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40774,7 +40774,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -40783,13 +40783,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="O230" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="R230" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.02034177074266263</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -40822,42 +40822,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40889,12 +40889,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -40928,93 +40928,81 @@
         </is>
       </c>
       <c r="N231" t="n">
+        <v>53</v>
+      </c>
+      <c r="O231" t="n">
+        <v>53</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="n">
         <v>0</v>
       </c>
-      <c r="O231" t="n">
-        <v>0</v>
-      </c>
-      <c r="P231" t="n">
-        <v>0</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO231" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP231" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT231" t="n">
-        <v>2</v>
-      </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41041,7 +41029,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -41093,98 +41081,18 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
@@ -41278,17 +41186,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41313,7 +41221,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -41322,81 +41230,173 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>92</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0.02635835082147835</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41428,12 +41428,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -41467,13 +41467,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="O234" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="R234" t="n">
-        <v>0.04900850445394597</v>
+        <v>0.02635835082147835</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -41506,42 +41506,42 @@
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41573,12 +41573,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -41612,93 +41612,81 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
-      </c>
-      <c r="P235" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="R235" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.04900850445394597</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41725,7 +41713,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -41777,98 +41765,18 @@
       <c r="P236" t="n">
         <v>1</v>
       </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R236" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
@@ -41962,17 +41870,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -41997,7 +41905,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -42006,81 +41914,173 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>134</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0.03839151097910976</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P237" t="n">
+        <v>1</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42112,12 +42112,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42142,7 +42142,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -42151,13 +42151,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="O238" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="R238" t="n">
-        <v>0.03675637834045948</v>
+        <v>0.03839151097910976</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -42190,42 +42190,42 @@
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42257,12 +42257,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42296,93 +42296,81 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O239" t="n">
-        <v>2</v>
-      </c>
-      <c r="P239" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="R239" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.03675637834045948</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42409,7 +42397,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -42461,98 +42449,18 @@
       <c r="P240" t="n">
         <v>2</v>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R240" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN240" t="b">
-        <v>1</v>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
@@ -42646,123 +42554,360 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>2</v>
+      </c>
+      <c r="O241" t="n">
+        <v>2</v>
+      </c>
+      <c r="P241" t="n">
+        <v>2</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>D107</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
         <is>
           <t>军团菌病</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="K242" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N241" t="n">
+      <c r="N242" t="n">
         <v>83</v>
       </c>
-      <c r="O241" t="n">
+      <c r="O242" t="n">
         <v>83</v>
       </c>
-      <c r="R241" t="n">
+      <c r="R242" t="n">
         <v>0.0237798165019859</v>
       </c>
-      <c r="S241" t="inlineStr">
+      <c r="S242" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO241" t="inlineStr">
+      <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP241" t="inlineStr">
+      <c r="AP242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR241" t="inlineStr">
+      <c r="AR242" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS241" t="inlineStr"/>
-      <c r="AT241" t="n">
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="n">
         <v>0</v>
       </c>
-      <c r="AU241" t="inlineStr">
+      <c r="AU242" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV241" t="inlineStr">
+      <c r="AV242" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW241" t="inlineStr">
+      <c r="AW242" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX241" t="inlineStr">
+      <c r="AX242" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY241" t="inlineStr">
+      <c r="AY242" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ241" t="inlineStr">
+      <c r="AZ242" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA241" t="inlineStr">
+      <c r="BA242" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB241" t="inlineStr">
+      <c r="BB242" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC241" t="inlineStr">
+      <c r="BC242" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -42884,7 +43029,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -42894,7 +43039,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -42946,7 +43091,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5400</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2164,17 +2174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2398,17 +2413,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2945,7 +2965,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2953,17 +2973,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3179,7 +3204,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3187,17 +3212,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -7077,7 +7107,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7085,17 +7115,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7311,7 +7346,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7319,17 +7354,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7760,7 +7800,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7768,17 +7808,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7994,7 +8039,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8002,17 +8047,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8549,7 +8599,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8557,17 +8607,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8783,7 +8838,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8791,17 +8846,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -12533,7 +12593,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -12541,17 +12601,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -12767,7 +12832,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12775,17 +12840,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -13216,7 +13286,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -13224,17 +13294,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -13450,7 +13525,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -13458,17 +13533,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -14005,7 +14085,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -14013,17 +14093,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -14239,7 +14324,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -14247,17 +14332,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -18380,7 +18470,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -18388,17 +18478,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -18614,7 +18709,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18622,17 +18717,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -19063,7 +19163,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -19071,17 +19171,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -19297,7 +19402,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -19305,17 +19410,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -19849,7 +19959,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -19857,17 +19967,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -20083,7 +20198,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -20091,17 +20206,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -23827,7 +23947,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23835,17 +23955,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -24061,7 +24186,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -24069,17 +24194,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -24510,7 +24640,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24518,17 +24648,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -24744,7 +24879,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24752,17 +24887,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -25296,7 +25436,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -25304,17 +25444,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -25530,7 +25675,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -25538,17 +25683,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -29816,7 +29966,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
@@ -29824,17 +29974,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS167" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -30050,7 +30205,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
@@ -30058,17 +30213,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS168" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -30499,7 +30659,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -30507,17 +30667,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS171" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -30733,7 +30898,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -30741,17 +30906,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -31285,7 +31455,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -31293,17 +31463,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -31519,7 +31694,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -31527,17 +31702,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -34704,7 +34884,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -34712,17 +34892,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS195" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -34938,7 +35123,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -34946,17 +35131,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -35387,7 +35577,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -35395,17 +35585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -35621,7 +35816,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -35629,17 +35824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -36173,7 +36373,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -36181,17 +36381,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS203" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -36407,7 +36612,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -36415,17 +36620,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS204" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -39737,7 +39947,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -39745,17 +39955,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS224" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -39971,7 +40186,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -39979,17 +40194,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS225" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -40275,7 +40495,7 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
@@ -40283,17 +40503,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS227" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -40509,7 +40734,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -40517,17 +40742,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS228" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -41621,13 +41621,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O236" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R236" t="n">
-        <v>0.1542580964198312</v>
+        <v>0.157930908239351</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -47143,13 +47143,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O269" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R269" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5775</v>
+        <v>5778</v>
       </c>
     </row>
     <row r="16">
